--- a/Reader/Model.xlsx
+++ b/Reader/Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2B7454FFAEBB5629/PythonWorks/ClassTable/Reader/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{AAEA2759-9BBF-4167-8C07-C97F94C486AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41C3B76-11D7-4EAE-838B-F610A25CE176}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{AAEA2759-9BBF-4167-8C07-C97F94C486AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540CF751-A4DF-44D4-B4D6-4E532FB95587}"/>
   <bookViews>
-    <workbookView xWindow="5800" yWindow="3480" windowWidth="22660" windowHeight="16540" xr2:uid="{334F784E-90E0-44B7-A569-F026F60E6228}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{334F784E-90E0-44B7-A569-F026F60E6228}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,15 +127,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>编辑颜色时修改对应单元格背景色即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（示例）XXXXX-XXXXX-XXXXX-XXXXX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>激活码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">编辑颜色时修改对应单元格背景色即可。                      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>请勿使用主题色！请使用标准颜色或自定义颜色！</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,7 +157,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,6 +195,15 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -243,7 +266,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -275,13 +298,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -324,14 +382,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -668,55 +735,56 @@
     <col min="19" max="19" width="37.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
       <c r="S1" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="N2" s="16" t="s">
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="13" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.3">
@@ -812,21 +880,11 @@
       <c r="R4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8">
-        <v>8</v>
-      </c>
-      <c r="C5" s="8">
-        <v>55</v>
-      </c>
-      <c r="D5" s="8">
-        <v>9</v>
-      </c>
-      <c r="E5" s="8">
-        <v>35</v>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -837,21 +895,11 @@
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
-        <v>3</v>
-      </c>
-      <c r="B6" s="8">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8">
-        <v>110</v>
-      </c>
-      <c r="D6" s="8">
-        <v>10</v>
-      </c>
-      <c r="E6" s="8">
-        <v>30</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -862,21 +910,11 @@
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8">
-        <v>8</v>
-      </c>
-      <c r="C7" s="8">
-        <v>165</v>
-      </c>
-      <c r="D7" s="8">
-        <v>11</v>
-      </c>
-      <c r="E7" s="8">
-        <v>25</v>
-      </c>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -887,21 +925,11 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
-        <v>5</v>
-      </c>
-      <c r="B8" s="8">
-        <v>8</v>
-      </c>
-      <c r="C8" s="8">
-        <v>220</v>
-      </c>
-      <c r="D8" s="8">
-        <v>12</v>
-      </c>
-      <c r="E8" s="8">
-        <v>20</v>
-      </c>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -912,21 +940,11 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8">
-        <v>275</v>
-      </c>
-      <c r="D9" s="8">
-        <v>13</v>
-      </c>
-      <c r="E9" s="8">
-        <v>15</v>
-      </c>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -937,21 +955,11 @@
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8">
-        <v>8</v>
-      </c>
-      <c r="C10" s="8">
-        <v>330</v>
-      </c>
-      <c r="D10" s="8">
-        <v>14</v>
-      </c>
-      <c r="E10" s="8">
-        <v>10</v>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -962,21 +970,11 @@
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8">
-        <v>8</v>
-      </c>
-      <c r="C11" s="8">
-        <v>385</v>
-      </c>
-      <c r="D11" s="8">
-        <v>15</v>
-      </c>
-      <c r="E11" s="8">
-        <v>5</v>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
